--- a/content/KPIM/campaigns.xlsx
+++ b/content/KPIM/campaigns.xlsx
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,36 +552,18 @@
           <t>CMP-2026-Q1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>KPIM Cashback Card</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>hitl</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>46028</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Team Marketing KPIM Bank</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>25</v>
       </c>
@@ -595,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,21 +582,9 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Số đăng ký mở thẻ</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Product, Education, Promo, HowTo, Testimonial, Brand</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>facebook, youtube</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CMP-2026-Q1</t>
@@ -630,36 +597,18 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vay Mua Nhà Ưu Đãi</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>46199</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-26</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Team Marketing KPIM Bank</t>
-        </is>
-      </c>
+          <t>hitl</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>26</v>
       </c>
@@ -670,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -678,21 +627,9 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Số hồ sơ vay</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Product, Education, Promo, HowTo, Testimonial, Brand</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>facebook, youtube</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CMP-2026-Q2</t>
@@ -705,36 +642,18 @@
           <t>CMP-2026-Q3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KPIM Digital &amp; Tiết Kiệm Online</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>hitl</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>46209</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="H4" t="n">
-        <v>65</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Team Marketing KPIM Bank</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>26</v>
       </c>
@@ -753,21 +672,9 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Số tải app / mở sổ</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Product, Education, Promo, HowTo, Testimonial, Brand</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>facebook, youtube</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CMP-2026-Q3</t>
@@ -780,36 +687,18 @@
           <t>CMP-2026-Q4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tài Khoản Lương &amp; Ưu Đãi Tết</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>hitl</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>46381</v>
-      </c>
-      <c r="H5" t="n">
-        <v>156</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Team Marketing KPIM Bank</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>25</v>
       </c>
@@ -828,21 +717,9 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Số mở tài khoản lương</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Product, Education, Promo, HowTo, Testimonial, Brand</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>facebook, youtube</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CMP-2026-Q4</t>

--- a/content/KPIM/campaigns.xlsx
+++ b/content/KPIM/campaigns.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaigns" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Campaigns'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Campaigns'!$A$1:$Q$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,6 +29,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -41,7 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -425,122 +426,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>campaign_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>campaign_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>campaign_name</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>campaign_type</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>pillar</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>automation_mode</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>schedule_start</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>days_left</t>
+          <t>schedule_end</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>num_posts_planned</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>assets_total</t>
+          <t>posts_total</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>assets_published</t>
+          <t>posts_published</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>assets_measured</t>
+          <t>gate_topic</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>gate_topic</t>
+          <t>gate_content</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>gate_content</t>
+          <t>gate_final</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>gate_final</t>
+          <t>kpi_targets</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>primary_kpi</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>pillars</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>channels</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
@@ -549,185 +538,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMP-2026-Q1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>01_Tobi_Posts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CMP-2026-06-TOBI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AI Agent cho người làm Data — nhập môn không buzzword</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hitl</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Duc Nguyen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>hitl</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>hitl</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>hitl</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>CMP-2026-Q4</t>
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Blog 500 views/bài, YouTube 200 views/video, FB 30 reactions/post</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Blog ducnguyen.vn (atlas), YouTube (Học cùng Tobi), Facebook (Tobi Nguyễn)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>01_Tobi_Posts</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:Q2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>